--- a/02_加值成品/生物/生物2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-3 人體的消化與吸收　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物2-3 人體的消化與吸收　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>把大分子分解成小分子是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>蠕動</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>化學消化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>消化</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>小腸</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>分解</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>主要吸收養分的器官是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>小腸</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>化學消化</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>絨毛</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>吸收</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>唾液中分解澱粉的酵素是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>小腸</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>絨毛</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>唾液澱粉酶</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>澱粉</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>胃分解蛋白質的酵素是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>唾液澱粉酶</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>附屬器官</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>胃蛋白酶</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>蛋白</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>小腸增大吸收面積的構造是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>絨毛</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>小腸</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>增面積</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>吸收水分形成糞便的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>大腸</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>小腸</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>蠕動</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>水分</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>食物進入身體的第一站是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>小腸</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>胃蛋白酶</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>口</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>口腔</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>消化分機械與？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>唾液澱粉酶</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>胃蛋白酶</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>化學消化</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>蠕動</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>兩類</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>膽汁由哪個器官分泌？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>蠕動</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>肝臟</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>附屬器官</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>附屬</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>消化道靠什麼運動推送食物？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>肝臟</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>蠕動</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>肌肉</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-3 人體的消化與吸收　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物2-3 人體的消化與吸收　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>消化系統順序？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>口食道胃小腸大腸</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>口咀嚼酵素初步分解經胃小腸酵素分解後小腸吸收</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>乳化脂肪增大接觸面積</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>微血管與乳糜管</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>路徑</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>絨毛的作用是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>增大吸收面積</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>唾液澱粉酶</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>附屬器官</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>小腸</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>增效</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>胃主要消化哪類養分？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>絨毛</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>蛋白質</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>大腸</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>胃蛋白酶</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>胃蛋白酶</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>小腸絨毛內有什麼運送養分？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>各酵素專一性且需特定環境</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>乳化脂肪增大接觸面積</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>微血管與乳糜管</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>口食道胃小腸大腸</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>吸收</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>大腸主要吸收？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>唾液澱粉酶</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>消化</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>水分</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>附屬器官</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>細嚼慢嚥有助？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>消化</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>絨毛</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>機械化學</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>肝與胰屬消化的？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>大腸</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>消化</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>附屬器官</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>水分</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>分泌</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>澱粉在口中初步被？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>口咀嚼酵素初步分解經胃小腸酵素分解後小腸吸收</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>唾液澱粉酶分解</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>過多便祕不足腹瀉</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>大量絨毛增大表面積並含血管運走養分</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>消化</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>胰臟分泌的消化液進入哪個器官？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>蠕動</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>肝臟</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>小腸</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>消化液</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>養分吸收後由什麼運送全身？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>大腸</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>胃蛋白酶</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>血液</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>運送</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-3 人體的消化與吸收　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物2-3 人體的消化與吸收　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明食物從口到吸收的完整消化過程？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>大量絨毛增大表面積並含血管運走養分</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>唾液澱粉酶分解</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>口咀嚼酵素初步分解經胃小腸酵素分解後小腸吸收</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>各酵素專一性且需特定環境</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>流程</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>小腸絨毛的構造如何提升吸收效率？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>機械磨碎增面積、化學酵素分解分子</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>食物無法分解吸收營養不良</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>大量絨毛增大表面積並含血管運走養分</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>口食道胃小腸大腸</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>設計</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何不同養分需不同酵素在不同器官消化？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>口咀嚼酵素初步分解經胃小腸酵素分解後小腸吸收</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>口食道胃小腸大腸</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>長且絨毛多表面積大</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>各酵素專一性且需特定環境</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>分工</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>比較機械消化與化學消化？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>微血管與乳糜管</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>口咀嚼酵素初步分解經胃小腸酵素分解後小腸吸收</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>機械磨碎增面積、化學酵素分解分子</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>各酵素專一性且需特定環境</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>大腸吸收水分不足或過多會如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>超過消化系統負荷</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>口咀嚼酵素初步分解經胃小腸酵素分解後小腸吸收</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>過多便祕不足腹瀉</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>唾液澱粉酶分解</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>健康</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>小腸為何是主要吸收場所？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>長且絨毛多表面積大</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>唾液澱粉酶分解</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>機械磨碎增面積、化學酵素分解分子</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>口食道胃小腸大腸</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>場所</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>消化酵素若失活對人體影響？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>各酵素專一性且需特定環境</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>唾液澱粉酶分解</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>食物無法分解吸收營養不良</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>機械磨碎增面積、化學酵素分解分子</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>失活</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>保護消化系統健康的方法？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>口咀嚼酵素初步分解經胃小腸酵素分解後小腸吸收</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>食物無法分解吸收營養不良</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>微血管與乳糜管</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>均衡飲食細嚼規律作息</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>保健</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>膽汁不含酵素卻助消化脂肪的原因？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>微血管與乳糜管</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>長且絨毛多表面積大</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>乳化脂肪增大接觸面積</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>口食道胃小腸大腸</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>乳化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>暴飲暴食為何易消化不良？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>超過消化系統負荷</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>唾液澱粉酶分解</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>口食道胃小腸大腸</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>長且絨毛多表面積大</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>保健</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>分解</t>
+          <t>分解作用：把體積大的食物分子分解成方便吸收的小分子，這個過程叫消化</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>吸收</t>
+          <t>主要吸收：小腸內壁布滿絨毛，是人體吸收養分最主要的器官</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>澱粉</t>
+          <t>分解澱粉：唾液中含有澱粉酶，能在口腔中就開始把澱粉分解成較小分子</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>蛋白</t>
+          <t>分解蛋白質：胃液中的胃蛋白酶能把食物中的蛋白質初步分解</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>增面積</t>
+          <t>增加面積：小腸內壁布滿許多細小的絨毛，能大幅增加吸收養分的表面積</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>水分</t>
+          <t>吸收水分：食物殘渣進入大腸後，水分被吸收，剩下的就形成糞便排出</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>口腔</t>
+          <t>消化起點：食物進入身體後，第一個經過並開始被消化的部位就是口腔</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>兩類</t>
+          <t>兩種方式：消化包含牙齒咀嚼等機械消化，以及酵素分解的化學消化</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>附屬</t>
+          <t>附屬：膽汁是由肝臟分泌、暫存在膽囊，屬於消化系統的附屬器官所產生的分泌物</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>肌肉</t>
+          <t>肌肉：消化道管壁的肌肉會規律收縮舒張，形成一波波的蠕動，把食物向前推送</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>路徑</t>
+          <t>消化路徑：食物依序經過口、食道、胃、小腸，最後到大腸，完成消化過程</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>增效</t>
+          <t>增加效率：絨毛讓小腸內壁表面積變大，能更有效率地吸收養分</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>胃蛋白酶</t>
+          <t>消化蛋白質：胃液中的胃蛋白酶主要負責把食物中的蛋白質分解</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>吸收</t>
+          <t>運送養分：絨毛內有微血管和乳糜管，能把吸收到的養分運送到全身</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>吸收水分：食物殘渣經過大腸時，大部分的水分會在這裡被身體吸收</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>機械化學</t>
+          <t>幫助消化：細嚼慢嚥能讓食物磨得更碎，並與唾液充分混合，有助後續消化</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>分泌</t>
+          <t>附屬器官：肝臟和胰臟雖不在消化道上，但會分泌消化液幫助消化，屬附屬器官</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>消化</t>
+          <t>初步分解：食物在口腔咀嚼時，唾液中的澱粉酶就開始把澱粉初步分解</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>消化液</t>
+          <t>消化液：胰臟分泌的胰液含有多種消化酵素，會經由胰管送入小腸，幫助分解各種養分</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>運送</t>
+          <t>運送：小腸吸收的養分進入微血管後，會隨著血液循環被運送到身體各處供細胞利用</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>流程</t>
+          <t>完整流程：食物先在口腔咀嚼並初步分解，經胃、小腸酵素進一步分解後，才在小腸被吸收</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>設計</t>
+          <t>構造巧妙：大量絨毛增大了小腸表面積，內部血管又能快速把養分運走，提升吸收效率</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>分工</t>
+          <t>各司其職：每種酵素只能分解特定養分，且需要合適的環境，所以要在不同器官作用</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>兩種消化：機械消化靠牙齒磨碎食物增加表面積，化學消化則靠酵素把分子分解</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>健康</t>
+          <t>影響健康：大腸吸收水分太多會造成便秘，吸收不足則容易導致腹瀉</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>場所</t>
+          <t>構造優勢：小腸長度長又布滿絨毛，表面積非常大，所以是主要的吸收場所</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>失活</t>
+          <t>影響嚴重：消化酵素失去作用會使食物無法被分解吸收，導致身體營養不良</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>保健</t>
+          <t>保健方法：均衡飲食、細嚼慢嚥並維持規律作息，都能幫助保護消化系統健康</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>乳化</t>
+          <t>乳化：膽汁本身不含消化酵素，但能把大團的脂肪乳化成許多小油滴，增加脂肪與酵素接觸的表面積，讓酵素能更有效地分解脂肪</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>保健</t>
+          <t>保健：短時間內吃下過多食物，超過消化系統能分泌的消化液與蠕動的處理能力，容易造成消化不良</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-3_三種難度測驗卷.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>蠕動</t>
+          <t>口</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>化學消化</t>
+          <t>蛋白質</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>小腸</t>
+          <t>唾液澱粉酶</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>胃蛋白酶</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>化學消化</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>唾液澱粉酶</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>胃蛋白酶</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>化學消化</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>蠕動</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>血液</t>
+          <t>小腸</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>蛋白質</t>
+          <t>大腸</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
